--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -1,37 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
+  <si>
+    <t>공정명</t>
+  </si>
+  <si>
+    <t>Filter명</t>
+  </si>
+  <si>
+    <t>Maker</t>
+  </si>
+  <si>
+    <t>Micron</t>
+  </si>
+  <si>
+    <t>현재고</t>
+  </si>
+  <si>
+    <t>사용중</t>
+  </si>
+  <si>
+    <t>10블럭</t>
+  </si>
+  <si>
+    <t>AR-F5203</t>
+  </si>
+  <si>
+    <t>신우</t>
+  </si>
+  <si>
+    <t>AR-F5103A</t>
+  </si>
+  <si>
+    <t>AR-F5103</t>
+  </si>
+  <si>
+    <t>PALL</t>
+  </si>
+  <si>
+    <t>AR-F5106 (12"x300#)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>7블럭</t>
+  </si>
+  <si>
+    <t>HP-F8701 (12"x300#)</t>
+  </si>
+  <si>
+    <t>HP-F8703 (12"x300#)</t>
+  </si>
+  <si>
+    <t>HP-F8701 필터같음</t>
+  </si>
+  <si>
+    <t>TG-F7103</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +125,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,326 +449,244 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>공정명</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Filter명</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Maker</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Micron</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>현재고</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>사용중</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>36</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
         <v>70</v>
       </c>
-      <c r="E4" t="n">
-        <v>240</v>
+      <c r="E4">
+        <v>120</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
         <v>70</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>120</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
         <v>50</v>
       </c>
-      <c r="E6" t="n">
-        <v>120</v>
+      <c r="E6">
+        <v>240</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
         <v>70</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>36</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AR-F5106 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>15</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HP-F8701 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>264</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HP-F8703 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HP-F8701 필터같음</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
         <v>40</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>18</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TG-F7103</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
         <v>50</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>30</v>
       </c>
       <c r="F12" t="b">
@@ -747,6 +694,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -1,116 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
-  <si>
-    <t>공정명</t>
-  </si>
-  <si>
-    <t>Filter명</t>
-  </si>
-  <si>
-    <t>Maker</t>
-  </si>
-  <si>
-    <t>Micron</t>
-  </si>
-  <si>
-    <t>현재고</t>
-  </si>
-  <si>
-    <t>사용중</t>
-  </si>
-  <si>
-    <t>10블럭</t>
-  </si>
-  <si>
-    <t>AR-F5203</t>
-  </si>
-  <si>
-    <t>신우</t>
-  </si>
-  <si>
-    <t>AR-F5103A</t>
-  </si>
-  <si>
-    <t>AR-F5103</t>
-  </si>
-  <si>
-    <t>PALL</t>
-  </si>
-  <si>
-    <t>AR-F5106 (12"x300#)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>7블럭</t>
-  </si>
-  <si>
-    <t>HP-F8701 (12"x300#)</t>
-  </si>
-  <si>
-    <t>HP-F8703 (12"x300#)</t>
-  </si>
-  <si>
-    <t>HP-F8701 필터같음</t>
-  </si>
-  <si>
-    <t>TG-F7103</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -449,244 +420,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>공정명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Filter명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>현재고</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>사용중</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>36</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>70</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>120</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>70</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>120</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>50</v>
       </c>
-      <c r="E6">
-        <v>240</v>
+      <c r="E6" t="n">
+        <v>120</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>70</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>36</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AR-F5106 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>15</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>264</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HP-F8703 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HP-F8701 필터같음</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>40</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>18</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>50</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>30</v>
       </c>
       <c r="F12" t="b">
@@ -694,8 +747,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -1,37 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="20">
+  <si>
+    <t>공정명</t>
+  </si>
+  <si>
+    <t>Filter명</t>
+  </si>
+  <si>
+    <t>Maker</t>
+  </si>
+  <si>
+    <t>Micron</t>
+  </si>
+  <si>
+    <t>현재고</t>
+  </si>
+  <si>
+    <t>사용중</t>
+  </si>
+  <si>
+    <t>10블럭</t>
+  </si>
+  <si>
+    <t>AR-F5203</t>
+  </si>
+  <si>
+    <t>신우</t>
+  </si>
+  <si>
+    <t>AR-F5103A</t>
+  </si>
+  <si>
+    <t>AR-F5103</t>
+  </si>
+  <si>
+    <t>PALL</t>
+  </si>
+  <si>
+    <t>AR-F5106 (12"x300#)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>7블럭</t>
+  </si>
+  <si>
+    <t>HP-F8701 (12"x300#)</t>
+  </si>
+  <si>
+    <t>HP-F8703 (12"x300#)</t>
+  </si>
+  <si>
+    <t>HP-F8701 필터같음</t>
+  </si>
+  <si>
+    <t>TG-F7103</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +125,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,326 +449,244 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>공정명</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Filter명</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Maker</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Micron</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>현재고</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>사용중</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>36</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
         <v>70</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>120</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
         <v>70</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>120</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
         <v>50</v>
       </c>
-      <c r="E6" t="n">
-        <v>240</v>
+      <c r="E6">
+        <v>120</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
         <v>70</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>36</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AR-F5106 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>15</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HP-F8701 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>264</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HP-F8703 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HP-F8701 필터같음</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
         <v>40</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>18</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TG-F7103</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
         <v>50</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>30</v>
       </c>
       <c r="F12" t="b">
@@ -747,6 +694,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -1,116 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="20">
-  <si>
-    <t>공정명</t>
-  </si>
-  <si>
-    <t>Filter명</t>
-  </si>
-  <si>
-    <t>Maker</t>
-  </si>
-  <si>
-    <t>Micron</t>
-  </si>
-  <si>
-    <t>현재고</t>
-  </si>
-  <si>
-    <t>사용중</t>
-  </si>
-  <si>
-    <t>10블럭</t>
-  </si>
-  <si>
-    <t>AR-F5203</t>
-  </si>
-  <si>
-    <t>신우</t>
-  </si>
-  <si>
-    <t>AR-F5103A</t>
-  </si>
-  <si>
-    <t>AR-F5103</t>
-  </si>
-  <si>
-    <t>PALL</t>
-  </si>
-  <si>
-    <t>AR-F5106 (12"x300#)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>7블럭</t>
-  </si>
-  <si>
-    <t>HP-F8701 (12"x300#)</t>
-  </si>
-  <si>
-    <t>HP-F8703 (12"x300#)</t>
-  </si>
-  <si>
-    <t>HP-F8701 필터같음</t>
-  </si>
-  <si>
-    <t>TG-F7103</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -449,244 +420,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>공정명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Filter명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>현재고</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>사용중</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>36</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>70</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>120</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>70</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>120</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>50</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>120</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>70</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>36</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AR-F5106 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>15</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>264</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>252</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HP-F8703 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HP-F8701 필터같음</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>40</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>18</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>50</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>30</v>
       </c>
       <c r="F12" t="b">
@@ -694,8 +747,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -532,7 +532,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
